--- a/Dropsense_V1/BOM(with images).xlsx
+++ b/Dropsense_V1/BOM(with images).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MISSION FALLOUT\DropSense\Dropsense_V1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEBF98D-F787-4E5B-A58C-8D753F53E323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B24515-1EBE-46EF-B854-A3748F355716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Component</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>TOTAL COST =</t>
+  </si>
+  <si>
+    <t>YIHUA 946D-IV Mini Soldering Hot Plate 400°C</t>
   </si>
 </sst>
 </file>
@@ -254,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -299,11 +302,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -361,6 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="15.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="99.33203125" customWidth="1"/>
@@ -1280,13 +1295,30 @@
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D24" s="4" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1</v>
+      </c>
+      <c r="C24" s="12">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20.37</v>
+      </c>
+      <c r="E24" s="17">
+        <v>20.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="5">
-        <f>SUM(E2:E21)+22.4</f>
-        <v>96.12</v>
+      <c r="E25" s="5">
+        <f>SUM(E2:E21)+22.4+20.37</f>
+        <v>116.49000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Dropsense_V1/BOM(with images).xlsx
+++ b/Dropsense_V1/BOM(with images).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MISSION FALLOUT\DropSense\Dropsense_V1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B24515-1EBE-46EF-B854-A3748F355716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06C59E-C33B-45B9-A6B1-8B5ABC988B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>Component</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>YIHUA 946D-IV Mini Soldering Hot Plate 400°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solder paste </t>
+  </si>
+  <si>
+    <t>https://babaocamachine.com/product/yihua-946d-iv-mini-soldering-hot-plate-400c-adjustable-temp-c-f-conversion/</t>
+  </si>
+  <si>
+    <t>https://makerbazar.in/products/mechanic-10cc-lead-free-no-clean-solder-flux-paste-syring?variant=48251101184240&amp;country=IN&amp;currency=INR&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;gad_source=1&amp;gad_campaignid=17426677322&amp;gbraid=0AAAAACLxaAYzTMmho7tyKRtryRSs-Y9Aj&amp;gclid=CjwKCAjwhLPOBhBiEiwA8_wJHASQQ-U7WRQD3fYT5-50Hm8-akhij7po16V3ck0qvIO8n_Q_sbHLIhoCsDsQAvD_BwE</t>
   </si>
 </sst>
 </file>
@@ -756,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="15.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="99.33203125" customWidth="1"/>
@@ -1311,12 +1320,35 @@
       <c r="E24" s="17">
         <v>20.37</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D25" s="4" t="s">
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1.8</v>
+      </c>
+      <c r="E25">
+        <v>1.8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E26" s="5">
         <f>SUM(E2:E21)+22.4+20.37</f>
         <v>116.49000000000001</v>
       </c>
